--- a/artfynd/A 38570-2024 artfynd.xlsx
+++ b/artfynd/A 38570-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17099549</v>
+        <v>17099548</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>809585.0474008882</v>
+        <v>809610</v>
       </c>
       <c r="R2" t="n">
-        <v>7255018.110296912</v>
+        <v>7255025</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2004-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2004-10-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -807,15 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17099548</v>
+        <v>17099549</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -847,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>809610.0724283711</v>
+        <v>809585</v>
       </c>
       <c r="R3" t="n">
-        <v>7255024.973807904</v>
+        <v>7255018</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,19 +860,9 @@
           <t>2004-10-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2004-10-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -942,12 +912,7 @@
         <v>17099550</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>809558.2465503376</v>
+        <v>809558</v>
       </c>
       <c r="R4" t="n">
-        <v>7255000.096257651</v>
+        <v>7255000</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,19 +977,9 @@
           <t>2004-10-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2004-10-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1074,12 +1029,7 @@
         <v>17079133</v>
       </c>
       <c r="B5" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>809574.2781908577</v>
+        <v>809574</v>
       </c>
       <c r="R5" t="n">
-        <v>7255024.139304837</v>
+        <v>7255024</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,19 +1094,9 @@
           <t>2012-07-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-07-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1191,12 +1131,7 @@
         <v>17079134</v>
       </c>
       <c r="B6" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>809421.9374502869</v>
+        <v>809422</v>
       </c>
       <c r="R6" t="n">
-        <v>7254887.859114687</v>
+        <v>7254888</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,19 +1196,9 @@
           <t>2012-07-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2012-07-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 38570-2024 artfynd.xlsx
+++ b/artfynd/A 38570-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17099548</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17099549</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17099550</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17079133</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,8 +1252,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17079134</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>